--- a/Allgemeine Daten/questionaire/answers_flea_ear.xlsx
+++ b/Allgemeine Daten/questionaire/answers_flea_ear.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/vorlesungen/Statistik/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/vorlesungen/Allgemeine Daten/questionaire/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83968147-0767-F744-ACA2-4E45A4437F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C4EC34-A419-344C-83A0-5CAD588140BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5080" yWindow="1860" windowWidth="28240" windowHeight="17240" xr2:uid="{4B0CAF44-59F9-924D-AB82-433A2D608263}"/>
   </bookViews>
@@ -63,9 +63,6 @@
     <t>Zufriedenheit des Infizierten</t>
   </si>
   <si>
-    <t>IQ des Flohs</t>
-  </si>
-  <si>
     <t>Flohschnupfen vom Floh</t>
   </si>
   <si>
@@ -75,9 +72,6 @@
     <t>Wie ist der allgemeine Ernährungszustand Ihres Flohs?</t>
   </si>
   <si>
-    <t>Welchen IQ-Score erreicht Ihr Floh in dem standardisierten Wechsler-Test?</t>
-  </si>
-  <si>
     <t>Lfd. Nr.</t>
   </si>
   <si>
@@ -115,6 +109,12 @@
   </si>
   <si>
     <t>schlecht</t>
+  </si>
+  <si>
+    <t>Wie weit springt Ihr Floh aus Ihrem Ohr?</t>
+  </si>
+  <si>
+    <t>Sprungweite</t>
   </si>
 </sst>
 </file>
@@ -495,18 +495,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32478866-8147-2644-8659-C5E920B7E74F}">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
         <v>5</v>
@@ -515,328 +516,344 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
       <c r="D2" s="1">
-        <f ca="1">_xlfn.NORM.INV(RAND(), 100, 15)</f>
-        <v>121.9287496182196</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(), 30.4, 9.1)</f>
+        <v>18.745600934905596</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="I2" s="1">
+        <f ca="1">AVERAGE(D2:D31)</f>
+        <v>28.710730952972998</v>
+      </c>
+      <c r="J2">
+        <f ca="1">_xlfn.STDEV.S(D2:D31)</f>
+        <v>9.337972848739005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1">
-        <f t="shared" ref="D3:D31" ca="1" si="0">_xlfn.NORM.INV(RAND(), 100, 15)</f>
-        <v>95.031109207639147</v>
+        <f t="shared" ref="D3:D31" ca="1" si="0">_xlfn.NORM.INV(RAND(), 30.4, 9.1)</f>
+        <v>22.024545823374698</v>
       </c>
       <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
         <v>21</v>
       </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="I3" s="1">
+        <f ca="1">AVERAGE(D32:D52)</f>
+        <v>24.409175962273718</v>
+      </c>
+      <c r="J3">
+        <f ca="1">_xlfn.STDEV.S(D32:D52)</f>
+        <v>9.8183586399941607</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
       <c r="D4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>89.416881431648179</v>
+        <v>22.967961888416333</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>103.0025702544331</v>
+        <v>29.825577443126335</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>139.22496312269442</v>
+        <v>25.735088352832626</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>105.77521644781908</v>
+        <v>22.664008386020996</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
       <c r="D8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>112.45113158685005</v>
+        <v>32.927151529979113</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
       <c r="D9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>88.454443195683922</v>
+        <v>10.571151502891514</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>92.996444265230849</v>
+        <v>18.660586406513801</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>102.82332479054205</v>
+        <v>26.499927036999278</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>31.06574933308114</v>
+      </c>
+      <c r="E12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>29.384168728357718</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>64.280900965881528</v>
-      </c>
-      <c r="E12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>128.88919400062272</v>
-      </c>
-      <c r="E13" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>112.12032231955267</v>
+        <v>25.663798261485848</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="1">
+        <f t="shared" ca="1" si="0"/>
+        <v>27.142455859074129</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="1">
-        <f t="shared" ca="1" si="0"/>
-        <v>73.946967439386498</v>
-      </c>
-      <c r="E15" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>126.33423516799637</v>
+        <v>40.5148445858607</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -844,20 +861,20 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>85.638537293984996</v>
+        <v>14.822627916015461</v>
       </c>
       <c r="E17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -865,20 +882,20 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>124.16367003945714</v>
+        <v>28.771288031217328</v>
       </c>
       <c r="E18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F18" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -886,20 +903,20 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" t="s">
         <v>13</v>
       </c>
-      <c r="C19" t="s">
-        <v>15</v>
-      </c>
       <c r="D19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>103.57014282243885</v>
+        <v>37.39541985854931</v>
       </c>
       <c r="E19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -907,20 +924,20 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D20" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>77.717086361012363</v>
+        <v>38.753094838298288</v>
       </c>
       <c r="E20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -928,20 +945,20 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D21" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>112.68345275877584</v>
+        <v>31.929422806990228</v>
       </c>
       <c r="E21" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -949,20 +966,20 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D22" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>110.88451290126385</v>
+        <v>50.557798697007378</v>
       </c>
       <c r="E22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -970,20 +987,20 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" t="s">
         <v>13</v>
       </c>
-      <c r="C23" t="s">
-        <v>15</v>
-      </c>
       <c r="D23" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>107.22917813048713</v>
+        <v>29.130072763009572</v>
       </c>
       <c r="E23" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F23" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -991,20 +1008,20 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D24" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>93.814134486434824</v>
+        <v>43.180975351384156</v>
       </c>
       <c r="E24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s">
         <v>21</v>
-      </c>
-      <c r="F24" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -1012,20 +1029,20 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D25" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>107.80858018373794</v>
+        <v>31.352866732797171</v>
       </c>
       <c r="E25" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -1033,20 +1050,20 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" t="s">
         <v>13</v>
       </c>
-      <c r="C26" t="s">
-        <v>15</v>
-      </c>
       <c r="D26" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>112.31201895582262</v>
+        <v>32.551512897650092</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
@@ -1054,20 +1071,20 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D27" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>98.835486419264555</v>
+        <v>39.502642682771146</v>
       </c>
       <c r="E27" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F27" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -1075,20 +1092,20 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D28" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>87.142210903192549</v>
+        <v>14.453291067563535</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -1096,20 +1113,20 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D29" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>96.201809800483403</v>
+        <v>32.108567534316379</v>
       </c>
       <c r="E29" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -1117,20 +1134,20 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D30" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>87.567695027785845</v>
+        <v>14.734026646906857</v>
       </c>
       <c r="E30" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F30" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -1138,20 +1155,20 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D31" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>95.474660666720339</v>
+        <v>37.685704691793063</v>
       </c>
       <c r="E31" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -1159,20 +1176,20 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D32" s="1">
-        <f ca="1">_xlfn.NORM.INV(RAND(), 110, 15)</f>
-        <v>103.76304129306358</v>
+        <f ca="1">_xlfn.NORM.INV(RAND(), 19.9, 9.1)</f>
+        <v>35.511592209472539</v>
       </c>
       <c r="E32" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -1180,20 +1197,20 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D33" s="1">
-        <f t="shared" ref="D33:D52" ca="1" si="1">_xlfn.NORM.INV(RAND(), 110, 15)</f>
-        <v>118.64484155193962</v>
+        <f t="shared" ref="D33:D52" ca="1" si="1">_xlfn.NORM.INV(RAND(), 19.9, 9.1)</f>
+        <v>15.55963418691789</v>
       </c>
       <c r="E33" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -1201,20 +1218,20 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D34" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>97.494855052144885</v>
+        <v>24.943791174372834</v>
       </c>
       <c r="E34" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -1222,20 +1239,20 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D35" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>107.05435070238347</v>
+        <v>23.734634962306458</v>
       </c>
       <c r="E35" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F35" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
@@ -1243,20 +1260,20 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D36" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>98.199613295426246</v>
+        <v>29.124857185454427</v>
       </c>
       <c r="E36" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F36" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
@@ -1264,20 +1281,20 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D37" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>96.506268892858728</v>
+        <v>30.410850603317225</v>
       </c>
       <c r="E37" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F37" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
@@ -1285,20 +1302,20 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D38" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>124.84781888383507</v>
+        <v>16.249560404964647</v>
       </c>
       <c r="E38" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
@@ -1306,20 +1323,20 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D39" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>111.42889022306696</v>
+        <v>37.463369500364458</v>
       </c>
       <c r="E39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39" t="s">
         <v>21</v>
-      </c>
-      <c r="F39" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -1327,20 +1344,20 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D40" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>135.01111042703022</v>
+        <v>32.162925524282656</v>
       </c>
       <c r="E40" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
@@ -1348,20 +1365,20 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D41" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>113.78026864877181</v>
+        <v>18.842415176185046</v>
       </c>
       <c r="E41" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -1369,20 +1386,20 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D42" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>111.65336695736696</v>
+        <v>13.266475511680731</v>
       </c>
       <c r="E42" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" t="s">
         <v>21</v>
-      </c>
-      <c r="F42" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -1390,20 +1407,20 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D43" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>114.87109229649148</v>
+        <v>19.913515234400226</v>
       </c>
       <c r="E43" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
@@ -1411,20 +1428,20 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D44" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>118.17537454499522</v>
+        <v>21.83584395541391</v>
       </c>
       <c r="E44" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
@@ -1432,20 +1449,20 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D45" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>128.69773183037316</v>
+        <v>27.379253740700516</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
@@ -1453,20 +1470,20 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D46" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>128.47148564952067</v>
+        <v>32.251827627639017</v>
       </c>
       <c r="E46" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
@@ -1474,20 +1491,20 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D47" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>113.68882618911425</v>
+        <v>20.529119521887797</v>
       </c>
       <c r="E47" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
@@ -1495,20 +1512,20 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D48" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>93.345126555897863</v>
+        <v>30.922019634294632</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F48" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
@@ -1516,20 +1533,20 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D49" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>79.218267852812048</v>
+        <v>21.679634982995193</v>
       </c>
       <c r="E49" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
@@ -1537,20 +1554,20 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D50" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>114.15026982863438</v>
+        <v>2.3066304022024013</v>
       </c>
       <c r="E50" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F50" t="s">
         <v>21</v>
-      </c>
-      <c r="F50" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
@@ -1558,20 +1575,20 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D51" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>103.72092706762427</v>
+        <v>45.340359136650292</v>
       </c>
       <c r="E51" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
@@ -1579,20 +1596,20 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D52" s="1">
         <f t="shared" ca="1" si="1"/>
-        <v>123.76033904988473</v>
+        <v>13.164384532245235</v>
       </c>
       <c r="E52" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
@@ -1639,15 +1656,15 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
@@ -1655,10 +1672,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
         <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
